--- a/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-005, 23-023, 24-010, 24-017, 24-018</t>
+          <t>24-005, 24-004, 23-016, 25-101, 25-120</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>7</v>
+      <c r="F9" s="9" t="n">
+        <v>9.6</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2.8-14.0</t>
+          <t>ratio=0.96 (0.80-1.54)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>17</v>
+      <c r="F10" s="9" t="n">
+        <v>25.6</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>5.0-93.5</t>
+          <t>ratio=1.82 (0.80-2.69)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,17 +794,17 @@
       <c r="E11" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>4</v>
+      <c r="F11" s="9" t="n">
+        <v>18</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>1.0-7.0</t>
+          <t>ratio=1.50 (0.25-2.00)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,8 +831,8 @@
       <c r="E12" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>1.8</v>
+      <c r="F12" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -843,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -870,8 +868,8 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>1.5</v>
+      <c r="F13" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -880,7 +878,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (0.50-2.00)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -907,8 +905,8 @@
       <c r="E14" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>1.2</v>
+      <c r="F14" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -917,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>1.0-7.0</t>
+          <t>ratio=1.12 (0.70-3.50)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -944,8 +942,8 @@
       <c r="E15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>5.5</v>
+      <c r="F15" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -954,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2.0-29.0</t>
+          <t>ratio=1.66 (1.50-2.25)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -981,8 +979,8 @@
       <c r="E16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>4.5</v>
+      <c r="F16" s="9" t="n">
+        <v>18.8</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -991,7 +989,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>2.0-9.8</t>
+          <t>ratio=3.75 (1.00-4.88)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1018,8 +1016,8 @@
       <c r="E17" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <v>11</v>
+      <c r="F17" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1028,7 +1026,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>global:11.0-11.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1055,8 +1053,8 @@
       <c r="E18" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <v>8</v>
+      <c r="F18" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1065,7 +1063,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>global:5.5-10.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1109,8 +1107,8 @@
       <c r="E20" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>39.5</v>
+      <c r="F20" s="9" t="n">
+        <v>132.4</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1119,7 +1117,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>36.0-122.5</t>
+          <t>ratio=1.89 (0.88-3.88)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1146,8 +1144,8 @@
       <c r="E21" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>12.8</v>
+      <c r="F21" s="9" t="n">
+        <v>22.6</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1156,7 +1154,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>9.5-14.5</t>
+          <t>ratio=0.65 (0.40-0.73)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1200,8 +1198,8 @@
       <c r="E23" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>2</v>
+      <c r="F23" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1210,7 +1208,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (0.40-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1237,8 +1235,8 @@
       <c r="E24" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>2</v>
+      <c r="F24" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1247,7 +1245,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-63.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1274,8 +1272,8 @@
       <c r="E25" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>5.8</v>
+      <c r="F25" s="9" t="n">
+        <v>62.7</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1284,7 +1282,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>3.0-6.0</t>
+          <t>ratio=1.31 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1312,7 +1310,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4.5</v>
+        <v>36</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1321,7 +1319,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>4.5-4.5</t>
+          <t>ratio=0.75 (n=1)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1366,12 +1364,12 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1416,12 +1414,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1448,8 +1446,8 @@
       <c r="E31" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>42</v>
+      <c r="F31" s="9" t="n">
+        <v>29.2</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1458,7 +1456,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>16.5-57.0</t>
+          <t>ratio=1.22 (1.06-2.60)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1485,8 +1483,8 @@
       <c r="E32" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>20</v>
+      <c r="F32" s="9" t="n">
+        <v>48</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1495,7 +1493,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>16.5-31.5</t>
+          <t>ratio=1.00 (0.39-1.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1522,8 +1520,8 @@
       <c r="E33" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>30.8</v>
+      <c r="F33" s="9" t="n">
+        <v>45.6</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1532,7 +1530,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>18.0-58.0</t>
+          <t>ratio=1.14 (0.50-3.70)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1576,17 +1574,17 @@
       <c r="E35" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>12</v>
+      <c r="F35" s="11" t="n">
+        <v>28</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>10.5-12.5</t>
+          <t>ratio=0.70 (n=1)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1611,17 +1609,15 @@
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
-      <c r="F36" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1648,8 +1644,8 @@
       <c r="E37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>4.5</v>
+      <c r="F37" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1658,7 +1654,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>2.0-32.0</t>
+          <t>ratio=3.50 (0.96-4.50)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1686,7 +1682,7 @@
         <v>30</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5.5</v>
+        <v>36.5</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>5.5-5.5</t>
+          <t>ratio=1.22 (n=2)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1723,7 +1719,7 @@
         <v>20</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1732,7 +1728,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>4.0-18.0</t>
+          <t>ratio=0.67 (n=2)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1777,7 +1773,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1786,7 +1782,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>26.0-26.0</t>
+          <t>ratio=1.40 (n=1)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1814,7 +1810,7 @@
         <v>30</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1823,7 +1819,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=0.67 (n=2)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1867,8 +1863,8 @@
       <c r="E44" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>13.5</v>
+      <c r="F44" s="9" t="n">
+        <v>81.2</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>4.0-41.0</t>
+          <t>ratio=0.81 (0.33-1.44)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1904,8 +1900,8 @@
       <c r="E45" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>23.5</v>
+      <c r="F45" s="9" t="n">
+        <v>112</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1914,7 +1910,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>19.5-28.5</t>
+          <t>ratio=1.40 (0.53-1.67)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1941,8 +1937,8 @@
       <c r="E46" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>32.8</v>
+      <c r="F46" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1951,7 +1947,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>23.0-42.5</t>
+          <t>ratio=1.00 (0.71-1.00)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1978,8 +1974,8 @@
       <c r="E47" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>8</v>
+      <c r="F47" s="9" t="n">
+        <v>70</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1988,7 +1984,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>2.5-29.0</t>
+          <t>ratio=1.75 (0.67-2.42)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2015,17 +2011,17 @@
       <c r="E48" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F48" s="9" t="n">
-        <v>2.8</v>
+      <c r="F48" s="11" t="n">
+        <v>42</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-276.8</t>
+          <t>ratio=0.70 (n=2)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2050,17 +2046,15 @@
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2087,8 +2081,8 @@
       <c r="E50" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>11.5</v>
+      <c r="F50" s="9" t="n">
+        <v>164</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2097,7 +2091,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>8.0-44.5</t>
+          <t>ratio=2.05 (0.80-3.00)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2125,7 +2119,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>11.5</v>
+        <v>52.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2134,7 +2128,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>8.5-14.5</t>
+          <t>ratio=1.05 (n=2)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2161,8 +2155,8 @@
       <c r="E52" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>67.8</v>
+      <c r="F52" s="9" t="n">
+        <v>146.2</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2171,7 +2165,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>21.5-114.5</t>
+          <t>ratio=1.22 (0.57-1.42)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2216,7 +2210,7 @@
         <v>60</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>68.8</v>
+        <v>65.8</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2225,7 +2219,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>41.5-96.0</t>
+          <t>ratio=1.10 (n=1)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2252,8 +2246,8 @@
       <c r="E55" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>45.5</v>
+      <c r="F55" s="9" t="n">
+        <v>31.5</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2262,7 +2256,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>16.0-76.5</t>
+          <t>ratio=1.12 (0.96-1.60)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2289,8 +2283,8 @@
       <c r="E56" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="F56" s="10" t="n">
-        <v>4.5</v>
+      <c r="F56" s="9" t="n">
+        <v>35</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2299,7 +2293,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>4.0-26.0</t>
+          <t>ratio=0.62 (0.53-0.73)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2326,8 +2320,8 @@
       <c r="E57" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="F57" s="10" t="n">
-        <v>17.5</v>
+      <c r="F57" s="9" t="n">
+        <v>87</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2336,7 +2330,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>8.5-40.5</t>
+          <t>ratio=0.72 (0.48-0.77)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2363,8 +2357,8 @@
       <c r="E58" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F58" s="10" t="n">
-        <v>3.5</v>
+      <c r="F58" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2373,7 +2367,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>1.5-10.0</t>
+          <t>ratio=1.00 (1.00-1.58)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2400,17 +2394,17 @@
       <c r="E59" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>5.2</v>
+      <c r="F59" s="11" t="n">
+        <v>37.5</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>5.0-16.0</t>
+          <t>ratio=0.62 (n=1)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2437,17 +2431,17 @@
       <c r="E60" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="10" t="n">
+      <c r="F60" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>0.5-3.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2491,8 +2485,8 @@
       <c r="E62" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="10" t="n">
-        <v>2</v>
+      <c r="F62" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2501,7 +2495,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1.0-11.5</t>
+          <t>ratio=1.00 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2526,17 +2520,15 @@
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2561,17 +2553,15 @@
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2615,8 +2605,8 @@
       <c r="E66" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F66" s="10" t="n">
-        <v>7.2</v>
+      <c r="F66" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2625,7 +2615,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>3.2-8.0</t>
+          <t>ratio=2.00 (0.65-4.25)</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2652,8 +2642,8 @@
       <c r="E67" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F67" s="9" t="n">
-        <v>5</v>
+      <c r="F67" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2662,7 +2652,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-8.0</t>
+          <t>wc_ratio=1.15</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2690,12 +2680,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2722,8 +2712,8 @@
       <c r="E69" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="F69" s="10" t="n">
-        <v>91</v>
+      <c r="F69" s="9" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2732,7 +2722,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>56.0-104.5</t>
+          <t>ratio=1.62 (0.35-1.88)</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2760,12 +2750,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2792,8 +2782,8 @@
       <c r="E71" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="9" t="n">
-        <v>3</v>
+      <c r="F71" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
@@ -2802,7 +2792,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-8.5</t>
+          <t>wc_ratio=1.50</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2830,12 +2820,12 @@
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2863,12 +2853,12 @@
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2912,8 +2902,8 @@
       <c r="E75" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F75" s="10" t="n">
-        <v>4.5</v>
+      <c r="F75" s="9" t="n">
+        <v>9.4</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2922,7 +2912,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>2.0-7.0</t>
+          <t>ratio=0.94 (0.20-1.50)</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2949,17 +2939,17 @@
       <c r="E76" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F76" s="10" t="n">
-        <v>3.5</v>
+      <c r="F76" s="11" t="n">
+        <v>4.5</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>3.5-4.0</t>
+          <t>ratio=0.90 (n=2)</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2987,12 +2977,12 @@
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I77" s="8" t="n"/>
@@ -3019,8 +3009,8 @@
       <c r="E78" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="F78" s="10" t="n">
-        <v>12</v>
+      <c r="F78" s="9" t="n">
+        <v>22.5</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
@@ -3029,7 +3019,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>5.0-19.0</t>
+          <t>ratio=0.90 (0.73-1.75)</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3056,8 +3046,8 @@
       <c r="E79" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F79" s="9" t="n">
-        <v>1.5</v>
+      <c r="F79" s="10" t="n">
+        <v>3.6</v>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
@@ -3066,7 +3056,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-1.5</t>
+          <t>wc_ratio=0.90</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3093,8 +3083,8 @@
       <c r="E80" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F80" s="9" t="n">
-        <v>3</v>
+      <c r="F80" s="10" t="n">
+        <v>3.6</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
@@ -3103,7 +3093,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-3.0</t>
+          <t>wc_ratio=0.90</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3117,7 +3107,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>740.5</v>
+        <v>1909.7</v>
       </c>
     </row>
   </sheetData>
@@ -3185,7 +3175,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-005, 23-023, 24-010, 24-017, 24-018</t>
+          <t>24-005, 24-004, 23-016, 25-101, 25-120</t>
         </is>
       </c>
     </row>
@@ -5176,28 +5166,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-023</t>
+          <t>24-004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-010</t>
+          <t>23-016</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-017</t>
+          <t>25-101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-018</t>
+          <t>25-120</t>
         </is>
       </c>
     </row>
@@ -5252,23 +5242,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5286,19 +5272,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-023, 24-005, 24-010, 24-017, 24-018</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5312,7 +5294,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5321,12 +5303,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.8-14.0</t>
+          <t>ratio=0.96 (0.80-1.54)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5324,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>25.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5351,12 +5333,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.0-93.5</t>
+          <t>ratio=1.82 (0.80-2.69)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5372,21 +5354,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0-7.0</t>
+          <t>ratio=1.50 (0.25-2.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5384,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5411,12 +5393,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5414,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5441,12 +5423,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (0.50-2.00)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5444,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5471,12 +5453,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-7.0</t>
+          <t>ratio=1.12 (0.70-3.50)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5474,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.5</v>
+        <v>9.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5501,12 +5483,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.0-29.0</t>
+          <t>ratio=1.66 (1.50-2.25)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5504,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.5</v>
+        <v>18.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5531,12 +5513,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.0-9.8</t>
+          <t>ratio=3.75 (1.00-4.88)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5534,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5561,12 +5543,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>global:11.0-11.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5564,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5591,12 +5573,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>global:5.5-10.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5594,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39.5</v>
+        <v>132.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5621,12 +5603,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>36.0-122.5</t>
+          <t>ratio=1.89 (0.88-3.88)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5624,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12.8</v>
+        <v>22.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5651,12 +5633,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9.5-14.5</t>
+          <t>ratio=0.65 (0.40-0.73)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005</t>
+          <t>25-101, 24-005, 24-004</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5654,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5681,12 +5663,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (0.40-1.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5684,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5711,12 +5693,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>global:1.0-63.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5714,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.8</v>
+        <v>62.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5741,12 +5723,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.0-6.0</t>
+          <t>ratio=1.31 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>25-101, 24-005, 23-016</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5744,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.5</v>
+        <v>36</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5771,7 +5753,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4.5-4.5</t>
+          <t>ratio=0.75 (n=1)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5796,19 +5778,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>23-023, 24-005, 24-017, 24-018</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5826,19 +5804,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>23-023, 24-005, 24-010, 24-017, 24-018</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5852,7 +5826,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>42</v>
+        <v>29.2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5861,12 +5835,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.5-57.0</t>
+          <t>ratio=1.22 (1.06-2.60)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5856,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5891,12 +5865,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16.5-31.5</t>
+          <t>ratio=1.00 (0.39-1.00)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 23-016</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5886,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>30.8</v>
+        <v>45.6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5921,12 +5895,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18.0-58.0</t>
+          <t>ratio=1.14 (0.50-3.70)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -5942,21 +5916,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.5-12.5</t>
+          <t>ratio=0.70 (n=1)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010</t>
+          <t>24-004</t>
         </is>
       </c>
     </row>
@@ -5972,23 +5946,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6002,7 +5972,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6011,12 +5981,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.0-32.0</t>
+          <t>ratio=3.50 (0.96-4.50)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6002,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.5</v>
+        <v>36.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6041,12 +6011,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.5-5.5</t>
+          <t>ratio=1.22 (n=2)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24-005</t>
+          <t>24-005, 24-004</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6032,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6071,12 +6041,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.0-18.0</t>
+          <t>ratio=0.67 (n=2)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24-010, 23-023</t>
+          <t>24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6062,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6101,12 +6071,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26.0-26.0</t>
+          <t>ratio=1.40 (n=1)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>24-010</t>
+          <t>24-004</t>
         </is>
       </c>
     </row>
@@ -6122,23 +6092,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6152,7 +6118,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6161,12 +6127,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=0.67 (n=2)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>24-005</t>
+          <t>25-101, 24-005</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6148,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13.5</v>
+        <v>81.2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6191,12 +6157,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.0-41.0</t>
+          <t>ratio=0.81 (0.33-1.44)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6178,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23.5</v>
+        <v>112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6221,12 +6187,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.5-28.5</t>
+          <t>ratio=1.40 (0.53-1.67)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6208,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>32.8</v>
+        <v>50</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6251,12 +6217,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23.0-42.5</t>
+          <t>ratio=1.00 (0.71-1.00)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6238,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6281,12 +6247,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.5-29.0</t>
+          <t>ratio=1.75 (0.67-2.42)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6302,21 +6268,21 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.8</v>
+        <v>42</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>global:0.5-276.8</t>
+          <t>ratio=0.70 (n=2)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-101, 23-016</t>
         </is>
       </c>
     </row>
@@ -6332,23 +6298,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6362,7 +6324,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11.5</v>
+        <v>164</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6371,12 +6333,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8.0-44.5</t>
+          <t>ratio=2.05 (0.80-3.00)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6354,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11.5</v>
+        <v>52.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6401,12 +6363,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8.5-14.5</t>
+          <t>ratio=1.05 (n=2)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>24-005, 23-023</t>
+          <t>24-005, 23-016</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6384,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>67.8</v>
+        <v>146.2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6431,12 +6393,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21.5-114.5</t>
+          <t>ratio=1.22 (0.57-1.42)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6414,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>68.8</v>
+        <v>65.8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,12 +6423,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>41.5-96.0</t>
+          <t>ratio=1.10 (n=1)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>24-010, 23-023</t>
+          <t>23-016</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6444,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>45.5</v>
+        <v>31.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6491,12 +6453,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16.0-76.5</t>
+          <t>ratio=1.12 (0.96-1.60)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6474,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.5</v>
+        <v>35</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,12 +6483,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4.0-26.0</t>
+          <t>ratio=0.62 (0.53-0.73)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6504,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.5</v>
+        <v>87</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6551,12 +6513,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8.5-40.5</t>
+          <t>ratio=0.72 (0.48-0.77)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6534,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.5</v>
+        <v>40</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6581,12 +6543,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5-10.0</t>
+          <t>ratio=1.00 (1.00-1.58)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6602,21 +6564,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5.2</v>
+        <v>37.5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5.0-16.0</t>
+          <t>ratio=0.62 (n=1)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005</t>
         </is>
       </c>
     </row>
@@ -6636,17 +6598,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.5-3.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-004</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6624,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,12 +6633,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.0-11.5</t>
+          <t>ratio=1.00 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6692,23 +6654,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6722,23 +6680,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6752,7 +6706,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6761,12 +6715,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3.2-8.0</t>
+          <t>ratio=2.00 (0.65-4.25)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6736,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6791,12 +6745,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>global:1.0-8.0</t>
+          <t>wc_ratio=1.15</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6816,19 +6770,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>23-023, 24-005, 24-010, 24-017, 24-018</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6842,7 +6792,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>91</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6851,12 +6801,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>56.0-104.5</t>
+          <t>ratio=1.62 (0.35-1.88)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>25-101, 24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -6876,19 +6826,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>23-023, 24-005, 24-010, 24-017, 24-018</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6902,7 +6848,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6911,12 +6857,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>global:0.5-8.5</t>
+          <t>wc_ratio=1.50</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6936,19 +6882,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>23-023, 24-010</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6966,19 +6908,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>23-023, 24-010</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6992,7 +6930,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7001,12 +6939,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2.0-7.0</t>
+          <t>ratio=0.94 (0.20-1.50)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -7022,21 +6960,21 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3.5-4.0</t>
+          <t>ratio=0.90 (n=2)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-005, 23-023</t>
+          <t>24-005, 24-004</t>
         </is>
       </c>
     </row>
@@ -7056,19 +6994,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>23-023, 24-005, 24-010, 24-017, 24-018</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7082,7 +7016,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>22.5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7091,12 +7025,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5.0-19.0</t>
+          <t>ratio=0.90 (0.73-1.75)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>24-018, 24-017, 24-010, 24-005, 23-023</t>
+          <t>24-005, 24-004, 23-016</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7046,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7121,12 +7055,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>global:1.5-1.5</t>
+          <t>wc_ratio=0.90</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7076,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7151,12 +7085,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>global:3.0-3.0</t>
+          <t>wc_ratio=0.90</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 25-101, 25-120</t>
+          <t>24-004, 24-005, 23-016, 25-101, 23-015</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.96 (0.80-1.54)</t>
+          <t>ratio=1.06 (0.80-1.57)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>25.6</v>
+        <v>26.6</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.82 (0.80-2.69)</t>
+          <t>ratio=1.90 (0.80-3.25)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -906,7 +906,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.70-3.50)</t>
+          <t>ratio=1.00 (0.70-3.50)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -943,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.66 (1.50-2.25)</t>
+          <t>ratio=1.81 (1.50-2.25)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -980,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>18.8</v>
+        <v>16.2</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.75 (1.00-4.88)</t>
+          <t>ratio=3.25 (1.00-4.88)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1108,7 +1108,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>132.4</v>
+        <v>126</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.89 (0.88-3.88)</t>
+          <t>ratio=1.80 (0.88-3.88)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1199,7 +1199,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.40-1.00)</t>
+          <t>ratio=0.75 (0.40-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1273,7 +1273,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>62.7</v>
+        <v>59.3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.31 (1.00-2.50)</t>
+          <t>ratio=1.24 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1310,7 +1310,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=1)</t>
+          <t>ratio=0.88 (n=2)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1447,7 +1447,7 @@
         <v>24</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.22 (1.06-2.60)</t>
+          <t>ratio=1.19 (1.06-2.60)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1521,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>45.6</v>
+        <v>55.6</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.14 (0.50-3.70)</t>
+          <t>ratio=1.39 (0.50-3.70)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>40</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=1)</t>
+          <t>ratio=1.02 (n=2)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1645,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.50 (0.96-4.50)</t>
+          <t>ratio=2.69 (0.96-4.50)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1773,7 +1773,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.40 (n=1)</t>
+          <t>ratio=1.20 (n=2)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1864,7 +1864,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>81.2</v>
+        <v>112.7</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.33-1.44)</t>
+          <t>ratio=1.13 (0.33-2.38)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1901,7 +1901,7 @@
         <v>80</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>112</v>
+        <v>122.7</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.53-1.67)</t>
+          <t>ratio=1.53 (0.53-2.00)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.71-1.00)</t>
+          <t>ratio=1.00 (0.71-2.57)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1975,7 +1975,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.67-2.42)</t>
+          <t>ratio=1.38 (0.67-2.42)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2082,7 +2082,7 @@
         <v>80</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>164</v>
+        <v>147.7</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.05 (0.80-3.00)</t>
+          <t>ratio=1.85 (0.80-3.00)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2156,7 +2156,7 @@
         <v>120</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>146.2</v>
+        <v>150.6</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.22 (0.57-1.42)</t>
+          <t>ratio=1.25 (0.57-1.42)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2210,7 +2210,7 @@
         <v>60</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>65.8</v>
+        <v>47.4</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (n=1)</t>
+          <t>ratio=0.79 (n=2)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2247,7 +2247,7 @@
         <v>28</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>31.5</v>
+        <v>29.1</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.96-1.60)</t>
+          <t>ratio=1.04 (0.69-1.60)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2284,7 +2284,7 @@
         <v>56</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.53-0.73)</t>
+          <t>ratio=0.68 (0.53-0.81)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2321,7 +2321,7 @@
         <v>120</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>87</v>
+        <v>72.2</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.72 (0.48-0.77)</t>
+          <t>ratio=0.60 (0.24-0.77)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2395,7 +2395,7 @@
         <v>60</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>37.5</v>
+        <v>101.2</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (n=1)</t>
+          <t>ratio=1.69 (n=2)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2606,7 +2606,7 @@
         <v>20</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>40</v>
+        <v>28.3</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (0.65-4.25)</t>
+          <t>ratio=1.42 (0.65-4.25)</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2643,7 +2643,7 @@
         <v>20</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.15</t>
+          <t>wc_ratio=1.20</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2713,7 +2713,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>81.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.35-1.88)</t>
+          <t>ratio=1.83 (0.35-2.51)</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2783,7 +2783,7 @@
         <v>4</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.50</t>
+          <t>wc_ratio=0.92</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2903,7 +2903,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>9.4</v>
+        <v>12.2</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.20-1.50)</t>
+          <t>ratio=1.22 (0.20-1.75)</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2939,17 +2939,17 @@
       <c r="E76" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F76" s="11" t="n">
-        <v>4.5</v>
+      <c r="F76" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (n=2)</t>
+          <t>ratio=1.00 (0.80-1.00)</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3010,7 +3010,7 @@
         <v>25</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>22.5</v>
+        <v>32.5</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.73-1.75)</t>
+          <t>ratio=1.30 (0.73-1.75)</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.90</t>
+          <t>wc_ratio=0.91</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.90</t>
+          <t>wc_ratio=0.91</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>1909.7</v>
+        <v>1979.3</v>
       </c>
     </row>
   </sheetData>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 25-101, 25-120</t>
+          <t>24-004, 24-005, 23-016, 25-101, 23-015</t>
         </is>
       </c>
     </row>
@@ -5159,14 +5159,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-005</t>
+          <t>24-004</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-004</t>
+          <t>24-005</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-120</t>
+          <t>23-015</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.96 (0.80-1.54)</t>
+          <t>ratio=1.06 (0.80-1.57)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.6</v>
+        <v>26.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5333,12 +5333,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.82 (0.80-2.69)</t>
+          <t>ratio=1.90 (0.80-3.25)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5453,12 +5453,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.70-3.50)</t>
+          <t>ratio=1.00 (0.70-3.50)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5483,12 +5483,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.66 (1.50-2.25)</t>
+          <t>ratio=1.81 (1.50-2.25)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.8</v>
+        <v>16.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5513,12 +5513,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=3.75 (1.00-4.88)</t>
+          <t>ratio=3.25 (1.00-4.88)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>132.4</v>
+        <v>126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.89 (0.88-3.88)</t>
+          <t>ratio=1.80 (0.88-3.88)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5663,12 +5663,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.40-1.00)</t>
+          <t>ratio=0.75 (0.40-1.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.7</v>
+        <v>59.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5723,12 +5723,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=1.31 (1.00-2.50)</t>
+          <t>ratio=1.24 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 23-016</t>
+          <t>25-101, 24-005, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=1)</t>
+          <t>ratio=0.88 (n=2)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>24-005</t>
+          <t>24-005, 23-015</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.22 (1.06-2.60)</t>
+          <t>ratio=1.19 (1.06-2.60)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>45.6</v>
+        <v>55.6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=1.14 (0.50-3.70)</t>
+          <t>ratio=1.39 (0.50-3.70)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5925,12 +5925,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=1)</t>
+          <t>ratio=1.02 (n=2)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24-004</t>
+          <t>24-004, 23-015</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=3.50 (0.96-4.50)</t>
+          <t>ratio=2.69 (0.96-4.50)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.40 (n=1)</t>
+          <t>ratio=1.20 (n=2)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>24-004</t>
+          <t>24-004, 23-015</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>81.2</v>
+        <v>112.7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.33-1.44)</t>
+          <t>ratio=1.13 (0.33-2.38)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>112</v>
+        <v>122.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.53-1.67)</t>
+          <t>ratio=1.53 (0.53-2.00)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.71-1.00)</t>
+          <t>ratio=1.00 (0.71-2.57)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,12 +6247,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.67-2.42)</t>
+          <t>ratio=1.38 (0.67-2.42)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>164</v>
+        <v>147.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6333,12 +6333,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=2.05 (0.80-3.00)</t>
+          <t>ratio=1.85 (0.80-3.00)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>146.2</v>
+        <v>150.6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6393,12 +6393,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=1.22 (0.57-1.42)</t>
+          <t>ratio=1.25 (0.57-1.42)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>65.8</v>
+        <v>47.4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=1.10 (n=1)</t>
+          <t>ratio=0.79 (n=2)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>23-016</t>
+          <t>23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>31.5</v>
+        <v>29.1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,12 +6453,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.96-1.60)</t>
+          <t>ratio=1.04 (0.69-1.60)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6483,12 +6483,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.53-0.73)</t>
+          <t>ratio=0.68 (0.53-0.81)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>87</v>
+        <v>72.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=0.72 (0.48-0.77)</t>
+          <t>ratio=0.60 (0.24-0.77)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37.5</v>
+        <v>101.2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=0.62 (n=1)</t>
+          <t>ratio=1.69 (n=2)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>24-005</t>
+          <t>24-005, 23-015</t>
         </is>
       </c>
     </row>
@@ -6603,12 +6603,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24-004</t>
+          <t>24-004, 23-015</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>28.3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,12 +6715,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ratio=2.00 (0.65-4.25)</t>
+          <t>ratio=1.42 (0.65-4.25)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>wc_ratio=1.15</t>
+          <t>wc_ratio=1.20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>81.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.35-1.88)</t>
+          <t>ratio=1.83 (0.35-2.51)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016</t>
+          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>wc_ratio=1.50</t>
+          <t>wc_ratio=0.92</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9.4</v>
+        <v>12.2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6939,12 +6939,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.20-1.50)</t>
+          <t>ratio=1.22 (0.20-1.75)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -6960,21 +6960,21 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ratio=0.90 (n=2)</t>
+          <t>ratio=1.00 (0.80-1.00)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>24-005, 24-004</t>
+          <t>24-005, 24-004, 23-015</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>22.5</v>
+        <v>32.5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.73-1.75)</t>
+          <t>ratio=1.30 (0.73-1.75)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016</t>
+          <t>24-005, 24-004, 23-016, 23-015</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>wc_ratio=0.90</t>
+          <t>wc_ratio=0.91</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>wc_ratio=0.90</t>
+          <t>wc_ratio=0.91</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">

--- a/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-004, 24-005, 23-016, 25-101, 23-015</t>
+          <t>24-005, 24-004, 23-016, 25-053, 25-101</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>10.6</v>
+        <v>23.7</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.80-1.57)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>26.6</v>
+        <v>49.6</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.90 (0.80-3.25)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -795,7 +788,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -804,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.25-2.00)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -832,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -841,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -869,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -878,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.00)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -906,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.70-3.50)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -943,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -952,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.81 (1.50-2.25)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -980,7 +973,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>16.2</v>
+        <v>9.6</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -989,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.25 (1.00-4.88)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1016,17 +1009,17 @@
       <c r="E17" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>10</v>
+      <c r="F17" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1053,17 +1046,17 @@
       <c r="E18" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>20</v>
+      <c r="F18" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1108,7 +1101,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>126</v>
+        <v>101.1</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1117,7 +1110,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.80 (0.88-3.88)</t>
+          <t>group_total:124h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1145,7 +1138,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1154,7 +1147,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.65 (0.40-0.73)</t>
+          <t>group_total:124h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1199,7 +1192,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>3</v>
+        <v>37.3</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1208,7 +1201,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-1.00)</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1235,17 +1228,17 @@
       <c r="E24" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>65</v>
+      <c r="F24" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1273,7 +1266,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>59.3</v>
+        <v>103.6</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1282,7 +1275,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.24 (1.00-2.50)</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1309,17 +1302,17 @@
       <c r="E26" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="F26" s="11" t="n">
-        <v>42</v>
+      <c r="F26" s="9" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (n=2)</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1364,12 +1357,12 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1414,12 +1407,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1447,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>28.5</v>
+        <v>33.9</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1456,7 +1449,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.19 (1.06-2.60)</t>
+          <t>group_total:73h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1484,7 +1477,7 @@
         <v>48</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>48</v>
+        <v>7.5</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1493,7 +1486,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.39-1.00)</t>
+          <t>group_total:73h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1521,7 +1514,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>55.6</v>
+        <v>31.3</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1530,7 +1523,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.39 (0.50-3.70)</t>
+          <t>group_total:73h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1574,17 +1567,17 @@
       <c r="E35" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>41</v>
+      <c r="F35" s="9" t="n">
+        <v>45</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.02 (n=2)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1612,12 +1605,12 @@
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1645,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>2.7</v>
+        <v>40</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1654,7 +1647,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.69 (0.96-4.50)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1681,17 +1674,17 @@
       <c r="E38" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>36.5</v>
+      <c r="F38" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.22 (n=2)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1718,17 +1711,17 @@
       <c r="E39" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F39" s="11" t="n">
-        <v>13.4</v>
+      <c r="F39" s="9" t="n">
+        <v>21.8</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=2)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1772,17 +1765,17 @@
       <c r="E41" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>24</v>
+      <c r="F41" s="9" t="n">
+        <v>178.5</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (n=2)</t>
+          <t>group_total:184h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1809,17 +1802,17 @@
       <c r="E42" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>20</v>
+      <c r="F42" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=2)</t>
+          <t>group_total:184h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1864,7 +1857,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>112.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1873,7 +1866,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.13 (0.33-2.38)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1901,7 +1894,7 @@
         <v>80</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>122.7</v>
+        <v>50.7</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1910,7 +1903,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.53 (0.53-2.00)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1938,7 +1931,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1947,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.71-2.57)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1975,7 +1968,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1984,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.38 (0.67-2.42)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2011,17 +2004,17 @@
       <c r="E48" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F48" s="11" t="n">
-        <v>42</v>
+      <c r="F48" s="9" t="n">
+        <v>35.5</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=2)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2049,12 +2042,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2082,7 +2075,7 @@
         <v>80</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>147.7</v>
+        <v>52.4</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2091,7 +2084,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.85 (0.80-3.00)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2118,17 +2111,17 @@
       <c r="E51" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="F51" s="11" t="n">
-        <v>52.5</v>
+      <c r="F51" s="9" t="n">
+        <v>26.4</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.05 (n=2)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2156,7 +2149,7 @@
         <v>120</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>150.6</v>
+        <v>121.5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2165,7 +2158,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.57-1.42)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2209,17 +2202,17 @@
       <c r="E54" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F54" s="11" t="n">
-        <v>47.4</v>
+      <c r="F54" s="9" t="n">
+        <v>83.5</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (n=2)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2247,7 +2240,7 @@
         <v>28</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>29.1</v>
+        <v>104</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2256,7 +2249,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.69-1.60)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2284,7 +2277,7 @@
         <v>56</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2293,7 +2286,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.68 (0.53-0.81)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2321,7 +2314,7 @@
         <v>120</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>72.2</v>
+        <v>103.3</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2330,7 +2323,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.60 (0.24-0.77)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2358,7 +2351,7 @@
         <v>40</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>40</v>
+        <v>31.3</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2367,7 +2360,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.58)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2394,17 +2387,17 @@
       <c r="E59" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F59" s="11" t="n">
-        <v>101.2</v>
+      <c r="F59" s="9" t="n">
+        <v>12.7</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.69 (n=2)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2431,17 +2424,17 @@
       <c r="E60" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="11" t="n">
-        <v>1</v>
+      <c r="F60" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2486,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>1</v>
+        <v>11.4</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2495,7 +2488,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-5.00)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2523,12 +2516,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2556,12 +2549,12 @@
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2606,7 +2599,7 @@
         <v>20</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>28.3</v>
+        <v>12.5</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2615,7 +2608,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.42 (0.65-4.25)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2642,17 +2635,17 @@
       <c r="E67" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>24</v>
+      <c r="F67" s="9" t="n">
+        <v>0.6</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.20</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2680,12 +2673,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2713,7 +2706,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2722,7 +2715,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.83 (0.35-2.51)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2750,12 +2743,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2782,17 +2775,17 @@
       <c r="E71" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="10" t="n">
-        <v>3.7</v>
+      <c r="F71" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.92</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2820,12 +2813,12 @@
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2853,12 +2846,12 @@
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2903,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>12.2</v>
+        <v>19.7</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2912,7 +2905,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.22 (0.20-1.75)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2940,7 +2933,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2949,7 +2942,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-1.00)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2977,12 +2970,12 @@
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I77" s="8" t="n"/>
@@ -3010,7 +3003,7 @@
         <v>25</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>32.5</v>
+        <v>24.8</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
@@ -3019,7 +3012,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.30 (0.73-1.75)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3047,16 +3040,16 @@
         <v>4</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.91</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3084,16 +3077,16 @@
         <v>4</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.91</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3107,7 +3100,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>1979.3</v>
+        <v>1867.2</v>
       </c>
     </row>
   </sheetData>
@@ -3175,7 +3168,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-004, 24-005, 23-016, 25-101, 23-015</t>
+          <t>24-005, 24-004, 23-016, 25-053, 25-101</t>
         </is>
       </c>
     </row>
@@ -5159,14 +5152,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-004</t>
+          <t>24-005</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-005</t>
+          <t>24-004</t>
         </is>
       </c>
     </row>
@@ -5180,14 +5173,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-101</t>
+          <t>25-053</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-015</t>
+          <t>25-101</t>
         </is>
       </c>
     </row>
@@ -5246,15 +5239,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5272,15 +5269,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5294,7 +5295,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.6</v>
+        <v>23.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5303,12 +5304,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.80-1.57)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5325,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.6</v>
+        <v>49.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5333,12 +5334,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.90 (0.80-3.25)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5355,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5363,12 +5364,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.25-2.00)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5385,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5393,12 +5394,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5415,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5423,12 +5424,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.00)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5445,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5453,12 +5454,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.70-3.50)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5475,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5483,12 +5484,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.81 (1.50-2.25)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5505,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.2</v>
+        <v>9.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5513,12 +5514,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=3.25 (1.00-4.88)</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5534,21 +5535,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5564,21 +5565,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5595,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>126</v>
+        <v>101.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5603,12 +5604,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.80 (0.88-3.88)</t>
+          <t>group_total:124h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5625,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5633,12 +5634,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=0.65 (0.40-0.73)</t>
+          <t>group_total:124h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5655,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>37.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5663,12 +5664,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-1.00)</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5684,21 +5685,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65</v>
+        <v>17.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5715,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>59.3</v>
+        <v>103.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5723,12 +5724,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=1.24 (1.00-2.50)</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 23-016, 23-015</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5744,21 +5745,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.88 (n=2)</t>
+          <t>group_total:228h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>24-005, 23-015</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5778,15 +5779,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5804,15 +5809,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5826,7 +5835,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.5</v>
+        <v>33.9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5835,12 +5844,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.19 (1.06-2.60)</t>
+          <t>group_total:73h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5865,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>48</v>
+        <v>7.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5865,12 +5874,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.39-1.00)</t>
+          <t>group_total:73h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 23-016</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5895,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55.6</v>
+        <v>31.3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5895,12 +5904,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=1.39 (0.50-3.70)</t>
+          <t>group_total:73h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5916,21 +5925,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.02 (n=2)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24-004, 23-015</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5950,15 +5959,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5972,7 +5985,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.7</v>
+        <v>40</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5981,12 +5994,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=2.69 (0.96-4.50)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6002,21 +6015,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>36.5</v>
+        <v>3.1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.22 (n=2)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24-005, 24-004</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6032,21 +6045,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13.4</v>
+        <v>21.8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=2)</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24-004, 23-016</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6062,21 +6075,21 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>178.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.20 (n=2)</t>
+          <t>group_total:184h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>24-004, 23-015</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6096,15 +6109,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6118,21 +6135,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=2)</t>
+          <t>group_total:184h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-101, 24-005</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6165,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>112.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6157,12 +6174,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.13 (0.33-2.38)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6195,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>122.7</v>
+        <v>50.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6187,12 +6204,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.53 (0.53-2.00)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6225,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6217,12 +6234,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.71-2.57)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6255,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,12 +6264,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.38 (0.67-2.42)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6268,21 +6285,21 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>42</v>
+        <v>35.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=2)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-101, 23-016</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6302,15 +6319,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6324,7 +6345,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>147.7</v>
+        <v>52.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6333,12 +6354,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=1.85 (0.80-3.00)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6354,21 +6375,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>52.5</v>
+        <v>26.4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.05 (n=2)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>24-005, 23-016</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6405,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>150.6</v>
+        <v>121.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6393,12 +6414,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.57-1.42)</t>
+          <t>group_total:454h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6414,21 +6435,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>47.4</v>
+        <v>83.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.79 (n=2)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>23-016, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6465,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>29.1</v>
+        <v>104</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,12 +6474,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.69-1.60)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6495,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6483,12 +6504,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=0.68 (0.53-0.81)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6525,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>72.2</v>
+        <v>103.3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6513,12 +6534,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=0.60 (0.24-0.77)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6555,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>40</v>
+        <v>31.3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6543,12 +6564,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.58)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6564,21 +6585,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>101.2</v>
+        <v>12.7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.69 (n=2)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>24-005, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6594,21 +6615,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24-004, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6645,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>11.4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6633,12 +6654,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-5.00)</t>
+          <t>group_total:405h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6658,15 +6679,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6684,15 +6709,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6706,7 +6735,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>28.3</v>
+        <v>12.5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,12 +6744,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ratio=1.42 (0.65-4.25)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6736,21 +6765,21 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24</v>
+        <v>0.6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>wc_ratio=1.20</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6770,15 +6799,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6792,7 +6825,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>91.40000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6801,12 +6834,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ratio=1.83 (0.35-2.51)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-101, 24-005, 24-004, 23-016, 23-015</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6826,15 +6859,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6848,21 +6885,21 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>wc_ratio=0.92</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6882,15 +6919,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6908,15 +6949,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6930,7 +6975,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12.2</v>
+        <v>19.7</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6939,12 +6984,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ratio=1.22 (0.20-1.75)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6960,7 +7005,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6969,12 +7014,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-1.00)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-015</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6994,15 +7039,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7016,7 +7065,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>32.5</v>
+        <v>24.8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7025,12 +7074,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ratio=1.30 (0.73-1.75)</t>
+          <t>group_total:167h</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>24-005, 24-004, 23-016, 23-015</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -7046,21 +7095,21 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>wc_ratio=0.91</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -7076,21 +7125,21 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>wc_ratio=0.91</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>nan</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-089 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>49.6</v>
+        <v>48.3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -788,7 +788,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -825,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -899,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -936,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -973,7 +973,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1101,7 +1101,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>101.1</v>
+        <v>103.7</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>group_total:124h</t>
+          <t>group_total:128h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1138,7 +1138,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:124h</t>
+          <t>group_total:128h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1192,7 +1192,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>37.3</v>
+        <v>34.6</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1229,7 +1229,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1266,7 +1266,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>103.6</v>
+        <v>96.2</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>69.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1440,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:73h</t>
+          <t>group_total:70h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1477,7 +1477,7 @@
         <v>48</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:73h</t>
+          <t>group_total:70h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1514,7 +1514,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:73h</t>
+          <t>group_total:70h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>40</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1638,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1712,7 +1712,7 @@
         <v>20</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1766,7 +1766,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>178.5</v>
+        <v>177.1</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:184h</t>
+          <t>group_total:182h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:184h</t>
+          <t>group_total:182h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1857,7 +1857,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>87.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1894,7 +1894,7 @@
         <v>80</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>50.7</v>
+        <v>52</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2005,7 +2005,7 @@
         <v>60</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>35.5</v>
+        <v>36.4</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2075,7 +2075,7 @@
         <v>80</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>52.4</v>
+        <v>53.7</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2112,7 +2112,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2149,7 +2149,7 @@
         <v>120</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>121.5</v>
+        <v>124.7</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2203,7 +2203,7 @@
         <v>60</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>83.5</v>
+        <v>87.5</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2240,7 +2240,7 @@
         <v>28</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>104</v>
+        <v>108.9</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2277,7 +2277,7 @@
         <v>56</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>52</v>
+        <v>54.4</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2314,7 +2314,7 @@
         <v>120</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>103.3</v>
+        <v>108.2</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2351,7 +2351,7 @@
         <v>40</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2388,7 +2388,7 @@
         <v>60</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2479,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2599,7 +2599,7 @@
         <v>20</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2706,7 +2706,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>102.9</v>
+        <v>101.8</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2896,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3003,7 +3003,7 @@
         <v>25</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>1867.2</v>
+        <v>1877.1</v>
       </c>
     </row>
   </sheetData>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>49.6</v>
+        <v>48.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:116h</t>
+          <t>group_total:113h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>101.1</v>
+        <v>103.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:124h</t>
+          <t>group_total:128h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:124h</t>
+          <t>group_total:128h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37.3</v>
+        <v>34.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>103.6</v>
+        <v>96.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>69.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:228h</t>
+          <t>group_total:212h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:73h</t>
+          <t>group_total:70h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:73h</t>
+          <t>group_total:70h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:73h</t>
+          <t>group_total:70h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:110h</t>
+          <t>group_total:111h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>178.5</v>
+        <v>177.1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:184h</t>
+          <t>group_total:182h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:184h</t>
+          <t>group_total:182h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>87.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50.7</v>
+        <v>52</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>35.5</v>
+        <v>36.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>52.4</v>
+        <v>53.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>121.5</v>
+        <v>124.7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:454h</t>
+          <t>group_total:465h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>83.5</v>
+        <v>87.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>104</v>
+        <v>108.9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>52</v>
+        <v>54.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>103.3</v>
+        <v>108.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>group_total:405h</t>
+          <t>group_total:424h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>102.9</v>
+        <v>101.8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>group_total:167h</t>
+          <t>group_total:165h</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
